--- a/Data Files/Backoffce/DistribuicaoPropostasGO/DistribuicaoPropostasGO.xlsx
+++ b/Data Files/Backoffce/DistribuicaoPropostasGO/DistribuicaoPropostasGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\DistribuicaoPropostasGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{7626C143-9FE3-443A-8AE8-705239931E79}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{99381276-CE4C-481E-BCC9-E91D9CA2DBD7}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
     <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" r:id="rId2" sheetId="8" state="hidden"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">DistribuicaoPropostasGO!$A$1:$L$53</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">DistribuicaoPropostasGO!$A$1:$L$126</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="221">
   <si>
     <t>NR PROPOSTA</t>
   </si>
@@ -418,673 +418,520 @@
     <t>114</t>
   </si>
   <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
     <t>Processado</t>
   </si>
   <si>
-    <t>29/01/2025 13:38
-  1017   (Nota)
-Mass.[MG/GO] 2024 - Bloqueio 888 BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:38
-  1023   (Nota)
-Mass.[INT. SP] 2024 - Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:39
-  1023   (Nota)
-Mass.[INT. SP] 2024 - Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:40
-  1017   (Nota)
-Mass.[MG/GO] 2024 - Bloqueio 888 BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:41
-  1038   (Nota)
-Mass.[ES/RJ] 2024 -Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:41
-  1032   (Nota)
-Mass.[Sul02] 2024 -Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:42
-  1023   (Nota)
-Mass.[INT. SP] 2024 - Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:43
-  1032   (Nota)
-Mass.[Sul02] 2024 -Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:44
-  1023   (Nota)
-Mass.[INT. SP] 2024 - Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:44
-  1029   (Nota)
-Mass.[Sul01] 2024 - Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:45
-  1020   (Nota)
-Mass.[N/NE] 2024 - Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:46
-  1020   (Nota)
-Mass.[N/NE] 2024 - Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:47
-  1038   (Nota)
-Mass.[ES/RJ] 2024 -Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:47
-  1014   (Nota)
-Mass.[SP] 2024 - Bloqueio 888 BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:48
-  1032   (Nota)
-Mass.[Sul02] 2024 -Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:49
-  1014   (Nota)
-Mass.[SP] 2024 - Bloqueio 888 BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:50
-  1023   (Nota)
-Mass.[INT. SP] 2024 - Bloqueio 888 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:50
-  1013   (Nota)
-Mass.[SP] 2024 - Bloqueio 714 BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:51
-  1034   (Nota)
-Mass.[PARC] 2024 -Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:52
-  1034   (Nota)
-Mass.[PARC] 2024 -Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:53
-  1013   (Nota)
-Mass.[SP] 2024 - Bloqueio 714 BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:53
-  1034   (Nota)
-Mass.[PARC] 2024 -Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:54
-  1022   (Nota)
-Mass.[INT. SP] 2024 - Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:55
-  1031   (Nota)
-Mass.[Sul02] 2024 -Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:56
-  1031   (Nota)
-Mass.[Sul02] 2024 -Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:56
-  1013   (Nota)
-Mass.[SP] 2024 - Bloqueio 714 BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:57
-  1016   (Nota)
-Mass.[MG/GO] 2024 - Bloqueio 714 BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:58
-  1028   (Nota)
-Mass.[Sul01] 2024 -Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:59
-  1019   (Nota)
-Mass.[N/NE] 2024 - Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 13:59
-  1031   (Nota)
-Mass.[Sul02] 2024 -Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:00
+    <t>Nota inválida</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:45
+  1027   (Nota)
+Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:45
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:46
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:47
   1015   (Nota)
 Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:01
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:48
+  1018   (Nota)
+Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:48
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:49
+  1027   (Nota)
+Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:50
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:51
   1030   (Nota)
 Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:02
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:51
+  1018   (Nota)
+Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:52
+  1027   (Nota)
+Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:53
+  1018   (Nota)
+Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:54
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:55
+  1030   (Nota)
+Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:56
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:57
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:57
+  1012   (Nota)
+Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:58
+  1033   (Nota)
+Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 19:59
+  1030   (Nota)
+Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:00
+  1027   (Nota)
+Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:01
+  1027   (Nota)
+Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:01
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:02
+  1027   (Nota)
+Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:03
+  1030   (Nota)
+Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:04
+  1030   (Nota)
+Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:04
+  1018   (Nota)
+Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:05
+  1012   (Nota)
+Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:06
+  1012   (Nota)
+Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:07
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:08
+  1030   (Nota)
+Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:08
+  1018   (Nota)
+Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:09
+  1027   (Nota)
+Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:10
+  1018   (Nota)
+Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:11
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:11
   1036   (Nota)
 Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:02
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:12
+  1012   (Nota)
+Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:13
+  1030   (Nota)
+Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:14
+  1018   (Nota)
+Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:15
+  1036   (Nota)
+Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:16
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:17
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:18
+  1018   (Nota)
+Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:19
   1033   (Nota)
 Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:03
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:20
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:20
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:21
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:22
+  1036   (Nota)
+Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:23
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:24
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:25
+  1027   (Nota)
+Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:26
+  1012   (Nota)
+Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:26
+  1033   (Nota)
+Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:27
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:28
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:29
   1030   (Nota)
 Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:04
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:30
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:30
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:31
+  1027   (Nota)
+Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:32
+  1015   (Nota)
+Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:33
   1030   (Nota)
 Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:05
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:34
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:35
+  1012   (Nota)
+Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:36
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:36
+  1033   (Nota)
+Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:37
+  1036   (Nota)
+Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:38
+  1033   (Nota)
+Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:39
+  1018   (Nota)
+Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:39
   1015   (Nota)
 Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:05
-  1018   (Nota)
-Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:06
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:40
+  1030   (Nota)
+Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:41
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:42
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:42
+  1030   (Nota)
+Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:43
+  1033   (Nota)
+Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:44
+  1030   (Nota)
+Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:45
   1015   (Nota)
 Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:07
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:45
+  1021   (Nota)
+Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:46
   1012   (Nota)
 Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:08
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:47
   1012   (Nota)
 Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:08
-  1015   (Nota)
-Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:09
+  25/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:48
   1033   (Nota)
 Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:10
-  1021   (Nota)
-Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:11
-  1027   (Nota)
-Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:11
-  1021   (Nota)
-Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:12
-  1015   (Nota)
-Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:13
-  1018   (Nota)
-Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:14
-  1030   (Nota)
-Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:15
-  1033   (Nota)
-Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:15
-  1021   (Nota)
-Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:16
-  1018   (Nota)
-Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:17
+  26/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025 20:48
   1036   (Nota)
 Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:18
-  1027   (Nota)
-Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:18
-  1021   (Nota)
-Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:19
-  1033   (Nota)
-Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:20
-  1021   (Nota)
-Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:21
-  1015   (Nota)
-Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:22
-  1012   (Nota)
-Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:23
-  1027   (Nota)
-Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:24
-  1012   (Nota)
-Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:24
-  1027   (Nota)
-Mass.[Sul01] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:25
-  1021   (Nota)
-Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:26
-  1036   (Nota)
-Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:27
-  1036   (Nota)
-Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:28
-  1036   (Nota)
-Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:29
-  1030   (Nota)
-Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:30
-  1036   (Nota)
-Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:30
-  1015   (Nota)
-Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:31
-  1030   (Nota)
-Mass.[Sul02] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:32
-  1012   (Nota)
-Mass.[SP] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:33
-  1036   (Nota)
-Mass.[ES/RJ] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:33
-  1033   (Nota)
-Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:34
-  1033   (Nota)
-Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:35
-  1033   (Nota)
-Mass.[PARC] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:36
-  1018   (Nota)
-Mass.[N/NE] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:36
-  1015   (Nota)
-Mass.[MG/GO] 2024 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:37
-  1021   (Nota)
-Mass.[INT. SP] 2024 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:38
-  1007   (Nota)
-Mass.[Sul02] 2002 - Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:39
-  1007   (Nota)
-Mass.[Sul02] 2002 - Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:39
-  1005   (Nota)
-Mass.[Sul01] 2002 - Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:40
-  999   (Nota)
-Mass.[N/NE] 2002 - Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:41
-  1007   (Nota)
-Mass.[Sul02] 2002 - Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:42
-  999   (Nota)
-Mass.[N/NE] 2002 - Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:42
-  995   (Nota)
-Mass.[SP] 2002 - Bloqueio 714 BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:43
-  999   (Nota)
-Mass.[N/NE] 2002 - Bloqueio 714 BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:46
-  1000   (Nota)
-Mass.[INT. SP] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:47
-  1010   (Nota)
-Mass.[ES/RJ] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:47
-  1004   (Nota)
-Mass.[Sul01] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:48
-  1010   (Nota)
-Mass.[ES/RJ] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:49
-  998   (Nota)
-Mass.[N/NE] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:50
-  1006   (Nota)
-Mass.[Sul02] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:50
-  996   (Nota)
-Mass.[MG/GO] 2002 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:51
-  1006   (Nota)
-Mass.[Sul02] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:52
-  996   (Nota)
-Mass.[MG/GO] 2002 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:53
-  1010   (Nota)
-Mass.[ES/RJ] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:53
-  1008   (Nota)
-Mass.[PARC] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:54
-  998   (Nota)
-Mass.[N/NE] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:55
-  1006   (Nota)
-Mass.[Sul02] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:56
-  1004   (Nota)
-Mass.[Sul01] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:56
-  1006   (Nota)
-Mass.[Sul02] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:57
-  1006   (Nota)
-Mass.[Sul02] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:58
-  1004   (Nota)
-Mass.[Sul01] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 14:59
-  998   (Nota)
-Mass.[N/NE] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 15:00
-  998   (Nota)
-Mass.[N/NE] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 15:01
-  1010   (Nota)
-Mass.[ES/RJ] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 15:02
-  1010   (Nota)
-Mass.[ES/RJ] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 15:02
-  996   (Nota)
-Mass.[MG/GO] 2002 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 15:03
-  1010   (Nota)
-Mass.[ES/RJ] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 15:04
-  996   (Nota)
-Mass.[MG/GO] 2002 - Demais Bloqueios BE53298     Publico
-  31/01/2025</t>
-  </si>
-  <si>
-    <t>29/01/2025 15:05
-  1010   (Nota)
-Mass.[ES/RJ] 2002 - Demais Bloqueios BE53298     Publico
-  03/02/2025</t>
+  26/03/2025</t>
   </si>
 </sst>
 </file>
@@ -1794,7 +1641,7 @@
   <sheetPr codeName="Planilha1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="13.7109375" collapsed="true"/>
@@ -1850,7 +1697,7 @@
     </row>
     <row customFormat="1" r="2" s="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>888195101</v>
+        <v>131703258</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1862,27 +1709,27 @@
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H2">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>888195105</v>
+        <v>131669977</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1891,27 +1738,27 @@
         <v>2024</v>
       </c>
       <c r="G3" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H3">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>888195111</v>
+        <v>131673685</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1920,27 +1767,27 @@
         <v>2024</v>
       </c>
       <c r="G4" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H4">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>11</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>888195113</v>
+        <v>131759889</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1949,27 +1796,27 @@
         <v>2024</v>
       </c>
       <c r="G5" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H5">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>888195119</v>
+        <v>131682091</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1978,27 +1825,27 @@
         <v>2024</v>
       </c>
       <c r="G6" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H6">
-        <v>1038</v>
+        <v>1018</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>888195126</v>
+        <v>131686911</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2007,27 +1854,27 @@
         <v>2024</v>
       </c>
       <c r="G7" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H7">
-        <v>1032</v>
+        <v>1015</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>14</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>888195129</v>
+        <v>131688504</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2036,27 +1883,27 @@
         <v>2024</v>
       </c>
       <c r="G8" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H8">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>15</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>888195143</v>
+        <v>131693506</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2065,27 +1912,27 @@
         <v>2024</v>
       </c>
       <c r="G9" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H9">
-        <v>1032</v>
+        <v>1015</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>888195149</v>
+        <v>131695194</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2094,27 +1941,27 @@
         <v>2024</v>
       </c>
       <c r="G10" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H10">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>888195152</v>
+        <v>131695249</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2123,27 +1970,27 @@
         <v>2024</v>
       </c>
       <c r="G11" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H11">
-        <v>1029</v>
+        <v>1018</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>888195156</v>
+        <v>131697010</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2152,27 +1999,27 @@
         <v>2024</v>
       </c>
       <c r="G12" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H12">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>19</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>888195157</v>
+        <v>131698927</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2181,27 +2028,27 @@
         <v>2024</v>
       </c>
       <c r="G13" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H13">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>20</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>888195158</v>
+        <v>131653984</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2210,27 +2057,27 @@
         <v>2024</v>
       </c>
       <c r="G14" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H14">
-        <v>1038</v>
+        <v>1021</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>888195160</v>
+        <v>131700997</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2239,27 +2086,27 @@
         <v>2024</v>
       </c>
       <c r="G15" s="3">
-        <v>888</v>
-      </c>
-      <c r="H15">
-        <v>1014</v>
+        <v>1701</v>
+      </c>
+      <c r="H15" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>888195171</v>
+        <v>131706692</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2268,27 +2115,27 @@
         <v>2024</v>
       </c>
       <c r="G16" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H16">
-        <v>1032</v>
+        <v>1021</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>888195172</v>
+        <v>131707364</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2297,27 +2144,27 @@
         <v>2024</v>
       </c>
       <c r="G17" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H17">
-        <v>1014</v>
+        <v>1030</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>24</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>888195181</v>
+        <v>131713825</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2326,27 +2173,27 @@
         <v>2024</v>
       </c>
       <c r="G18" s="3">
-        <v>888</v>
+        <v>1701</v>
       </c>
       <c r="H18">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>130999938</v>
+        <v>131715143</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2355,27 +2202,27 @@
         <v>2024</v>
       </c>
       <c r="G19" s="3">
-        <v>714</v>
-      </c>
-      <c r="H19">
-        <v>1013</v>
+        <v>1701</v>
+      </c>
+      <c r="H19" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>131003289</v>
+        <v>131719281</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2384,27 +2231,27 @@
         <v>2024</v>
       </c>
       <c r="G20" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H20">
-        <v>1034</v>
+        <v>1021</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>27</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>131003541</v>
+        <v>131720742</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2413,27 +2260,27 @@
         <v>2024</v>
       </c>
       <c r="G21" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H21">
-        <v>1034</v>
+        <v>1012</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>131003569</v>
+        <v>131720931</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2442,27 +2289,27 @@
         <v>2024</v>
       </c>
       <c r="G22" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H22">
-        <v>1013</v>
+        <v>1033</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>29</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>131008132</v>
+        <v>131721533</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2471,27 +2318,27 @@
         <v>2024</v>
       </c>
       <c r="G23" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H23">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>131008140</v>
+        <v>131722435</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2500,27 +2347,27 @@
         <v>2024</v>
       </c>
       <c r="G24" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H24">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>31</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>131008172</v>
+        <v>131722752</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2529,27 +2376,27 @@
         <v>2024</v>
       </c>
       <c r="G25" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H25">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>32</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>131011605</v>
+        <v>131723677</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2558,27 +2405,27 @@
         <v>2024</v>
       </c>
       <c r="G26" s="3">
-        <v>714</v>
-      </c>
-      <c r="H26">
-        <v>1031</v>
+        <v>1701</v>
+      </c>
+      <c r="H26" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>33</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>131012271</v>
+        <v>131725988</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2587,27 +2434,27 @@
         <v>2024</v>
       </c>
       <c r="G27" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H27">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>34</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>131012654</v>
+        <v>131726373</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2616,27 +2463,27 @@
         <v>2024</v>
       </c>
       <c r="G28" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H28">
-        <v>1016</v>
+        <v>1027</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>35</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>131014225</v>
+        <v>131726419</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2645,27 +2492,27 @@
         <v>2024</v>
       </c>
       <c r="G29" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H29">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>36</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>131015895</v>
+        <v>131726598</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2674,27 +2521,27 @@
         <v>2024</v>
       </c>
       <c r="G30" s="3">
-        <v>714</v>
-      </c>
-      <c r="H30">
-        <v>1019</v>
+        <v>1701</v>
+      </c>
+      <c r="H30" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>37</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>130998862</v>
+        <v>131726856</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2703,27 +2550,27 @@
         <v>2024</v>
       </c>
       <c r="G31" s="3">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H31">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>38</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>131000570</v>
+        <v>131727996</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2735,24 +2582,24 @@
         <v>1701</v>
       </c>
       <c r="H32">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>39</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>131014294</v>
+        <v>131730194</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2764,24 +2611,24 @@
         <v>1701</v>
       </c>
       <c r="H33">
-        <v>1030</v>
+        <v>1012</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>40</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>131018886</v>
+        <v>131731618</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2793,24 +2640,24 @@
         <v>1701</v>
       </c>
       <c r="H34">
-        <v>1036</v>
+        <v>1012</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>41</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>131023109</v>
+        <v>131732201</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2822,24 +2669,24 @@
         <v>1701</v>
       </c>
       <c r="H35">
-        <v>1033</v>
+        <v>1015</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>42</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>131026246</v>
+        <v>131732823</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2857,18 +2704,18 @@
         <v>65</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>43</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>131031591</v>
+        <v>131733553</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2880,24 +2727,24 @@
         <v>1701</v>
       </c>
       <c r="H37">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>44</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>131035339</v>
+        <v>131734171</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2909,24 +2756,24 @@
         <v>1701</v>
       </c>
       <c r="H38">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>45</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>131074444</v>
+        <v>131734248</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2944,18 +2791,18 @@
         <v>65</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>46</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>131036474</v>
+        <v>131734481</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2966,25 +2813,25 @@
       <c r="G40" s="3">
         <v>1701</v>
       </c>
-      <c r="H40">
-        <v>1015</v>
+      <c r="H40" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>47</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>131040998</v>
+        <v>131736321</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2996,24 +2843,24 @@
         <v>1701</v>
       </c>
       <c r="H41">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>48</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>131044389</v>
+        <v>131736999</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3025,24 +2872,24 @@
         <v>1701</v>
       </c>
       <c r="H42">
-        <v>1012</v>
+        <v>1036</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>49</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>131045061</v>
+        <v>131753569</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3054,24 +2901,24 @@
         <v>1701</v>
       </c>
       <c r="H43">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>50</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>131046956</v>
+        <v>131768510</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3083,24 +2930,24 @@
         <v>1701</v>
       </c>
       <c r="H44">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>51</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>131050162</v>
+        <v>131738912</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3112,24 +2959,24 @@
         <v>1701</v>
       </c>
       <c r="H45">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>52</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>131050572</v>
+        <v>131740143</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3141,24 +2988,24 @@
         <v>1701</v>
       </c>
       <c r="H46">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>53</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>131052339</v>
+        <v>131740218</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3170,24 +3017,24 @@
         <v>1701</v>
       </c>
       <c r="H47">
-        <v>1021</v>
+        <v>1036</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>54</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>131052729</v>
+        <v>131740951</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3199,24 +3046,24 @@
         <v>1701</v>
       </c>
       <c r="H48">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>55</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>131053019</v>
+        <v>131741732</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3228,24 +3075,24 @@
         <v>1701</v>
       </c>
       <c r="H49">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>56</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>131053123</v>
+        <v>131741938</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3256,25 +3103,25 @@
       <c r="G50" s="3">
         <v>1701</v>
       </c>
-      <c r="H50">
-        <v>1030</v>
+      <c r="H50" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>57</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>129632758</v>
+        <v>131743010</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3286,24 +3133,24 @@
         <v>1701</v>
       </c>
       <c r="H51">
-        <v>1033</v>
+        <v>1015</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>58</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>131056947</v>
+        <v>131743115</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3315,24 +3162,24 @@
         <v>1701</v>
       </c>
       <c r="H52">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>59</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>131057966</v>
+        <v>131744627</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3344,24 +3191,24 @@
         <v>1701</v>
       </c>
       <c r="H53">
-        <v>1018</v>
+        <v>1033</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>60</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>131061044</v>
+        <v>131744919</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3373,24 +3220,24 @@
         <v>1701</v>
       </c>
       <c r="H54">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>66</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>131062123</v>
+        <v>131745125</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3402,24 +3249,24 @@
         <v>1701</v>
       </c>
       <c r="H55">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>67</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>131063025</v>
+        <v>131745555</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3431,24 +3278,24 @@
         <v>1701</v>
       </c>
       <c r="H56">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>68</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>131066216</v>
+        <v>131746068</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3460,24 +3307,24 @@
         <v>1701</v>
       </c>
       <c r="H57">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>69</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>131067182</v>
+        <v>131747620</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3495,18 +3342,18 @@
         <v>65</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>70</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>131069201</v>
+        <v>131748667</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3518,24 +3365,24 @@
         <v>1701</v>
       </c>
       <c r="H59">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>71</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>131070826</v>
+        <v>131749056</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3547,24 +3394,24 @@
         <v>1701</v>
       </c>
       <c r="H60">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>72</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>131070937</v>
+        <v>131749293</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3575,25 +3422,25 @@
       <c r="G61">
         <v>1701</v>
       </c>
-      <c r="H61">
-        <v>1012</v>
+      <c r="H61" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>73</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>131071251</v>
+        <v>131752339</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3611,18 +3458,18 @@
         <v>65</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>74</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>131071364</v>
+        <v>131752972</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3633,25 +3480,25 @@
       <c r="G63">
         <v>1701</v>
       </c>
-      <c r="H63">
-        <v>1012</v>
+      <c r="H63" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>75</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>131071882</v>
+        <v>131753306</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3663,13 +3510,13 @@
         <v>1701</v>
       </c>
       <c r="H64">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>76</v>
@@ -3680,7 +3527,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>131074812</v>
+        <v>131753529</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3692,13 +3539,13 @@
         <v>1701</v>
       </c>
       <c r="H65">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>77</v>
@@ -3709,7 +3556,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>131076410</v>
+        <v>131753738</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3720,25 +3567,25 @@
       <c r="G66">
         <v>1701</v>
       </c>
-      <c r="H66">
-        <v>1036</v>
+      <c r="H66" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>78</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>131077858</v>
+        <v>131754449</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -3750,24 +3597,24 @@
         <v>1701</v>
       </c>
       <c r="H67">
-        <v>1036</v>
+        <v>1015</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>79</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>131079034</v>
+        <v>131754753</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -3779,13 +3626,13 @@
         <v>1701</v>
       </c>
       <c r="H68">
-        <v>1036</v>
+        <v>1015</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>80</v>
@@ -3796,7 +3643,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>131080690</v>
+        <v>131755567</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -3808,13 +3655,13 @@
         <v>1701</v>
       </c>
       <c r="H69">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>81</v>
@@ -3825,7 +3672,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>131082279</v>
+        <v>131756039</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -3837,13 +3684,13 @@
         <v>1701</v>
       </c>
       <c r="H70">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>82</v>
@@ -3854,7 +3701,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>131092333</v>
+        <v>131757861</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -3866,13 +3713,13 @@
         <v>1701</v>
       </c>
       <c r="H71">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>83</v>
@@ -3883,7 +3730,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>131087609</v>
+        <v>131781816</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -3895,13 +3742,13 @@
         <v>1701</v>
       </c>
       <c r="H72">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>84</v>
@@ -3912,7 +3759,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>131079563</v>
+        <v>131790535</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -3924,13 +3771,13 @@
         <v>1701</v>
       </c>
       <c r="H73">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>85</v>
@@ -3941,7 +3788,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>131128246</v>
+        <v>131759801</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -3950,16 +3797,16 @@
         <v>2024</v>
       </c>
       <c r="G74">
-        <v>2279</v>
+        <v>1701</v>
       </c>
       <c r="H74">
-        <v>1012</v>
+        <v>1030</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>86</v>
@@ -3970,7 +3817,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>131129092</v>
+        <v>131760238</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -3979,27 +3826,27 @@
         <v>2024</v>
       </c>
       <c r="G75">
-        <v>2279</v>
+        <v>1701</v>
       </c>
       <c r="H75">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>87</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>131132946</v>
+        <v>131760496</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -4008,27 +3855,27 @@
         <v>2024</v>
       </c>
       <c r="G76">
-        <v>2279</v>
+        <v>1701</v>
       </c>
       <c r="H76">
-        <v>1033</v>
+        <v>1021</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>88</v>
       </c>
       <c r="L76" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>131133194</v>
+        <v>131761251</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -4037,27 +3884,27 @@
         <v>2024</v>
       </c>
       <c r="G77">
-        <v>2279</v>
-      </c>
-      <c r="H77">
-        <v>1033</v>
+        <v>1701</v>
+      </c>
+      <c r="H77" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="L77" t="s">
-        <v>203</v>
+      <c r="L77" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>131135634</v>
+        <v>131762438</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -4066,27 +3913,27 @@
         <v>2024</v>
       </c>
       <c r="G78">
-        <v>2279</v>
-      </c>
-      <c r="H78">
-        <v>1033</v>
+        <v>1701</v>
+      </c>
+      <c r="H78" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="L78" t="s">
-        <v>204</v>
+      <c r="L78" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>131136981</v>
+        <v>131767969</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -4095,27 +3942,27 @@
         <v>2024</v>
       </c>
       <c r="G79">
-        <v>2279</v>
+        <v>1701</v>
       </c>
       <c r="H79">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>91</v>
       </c>
       <c r="L79" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>131138173</v>
+        <v>131769110</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -4124,27 +3971,27 @@
         <v>2024</v>
       </c>
       <c r="G80">
-        <v>2279</v>
+        <v>1701</v>
       </c>
       <c r="H80">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>92</v>
       </c>
       <c r="L80" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>131141037</v>
+        <v>131769855</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -4153,546 +4000,549 @@
         <v>2024</v>
       </c>
       <c r="G81">
-        <v>2279</v>
+        <v>1701</v>
       </c>
       <c r="H81">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>93</v>
       </c>
       <c r="L81" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>131000942</v>
+        <v>131773070</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G82">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H82">
-        <v>1007</v>
+        <v>1036</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>94</v>
       </c>
       <c r="L82" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>131011683</v>
+        <v>131774083</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G83">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H83">
-        <v>1007</v>
+        <v>1033</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>95</v>
       </c>
       <c r="L83" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>130999362</v>
+        <v>131775331</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G84">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H84">
-        <v>1005</v>
+        <v>1018</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>96</v>
       </c>
       <c r="L84" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>131001387</v>
+        <v>131776943</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G85">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H85">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>97</v>
       </c>
       <c r="L85" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>131004956</v>
+        <v>131778087</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
       <c r="C86">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G86">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H86">
-        <v>1007</v>
+        <v>1030</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>98</v>
       </c>
       <c r="L86" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>131007709</v>
+        <v>131780290</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G87">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H87">
-        <v>999</v>
+        <v>1021</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>99</v>
       </c>
       <c r="L87" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>131008758</v>
+        <v>128607275</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G88">
-        <v>714</v>
-      </c>
-      <c r="H88">
-        <v>995</v>
+        <v>1701</v>
+      </c>
+      <c r="H88" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="L88" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L88" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>131014204</v>
+        <v>131786191</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G89">
-        <v>714</v>
+        <v>1701</v>
       </c>
       <c r="H89">
-        <v>999</v>
+        <v>1021</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>101</v>
       </c>
       <c r="L89" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>131017827</v>
+        <v>131789748</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G90">
-        <v>714</v>
-      </c>
-      <c r="H90" t="e">
-        <v>#N/A</v>
+        <v>1701</v>
+      </c>
+      <c r="H90">
+        <v>1030</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L90" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>130999872</v>
+        <v>131797185</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G91">
         <v>1701</v>
       </c>
       <c r="H91">
-        <v>1000</v>
+        <v>1033</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>103</v>
       </c>
       <c r="L91" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>131003088</v>
+        <v>131803790</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G92">
         <v>1701</v>
       </c>
       <c r="H92">
-        <v>1010</v>
+        <v>1030</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>104</v>
       </c>
       <c r="L92" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>131005346</v>
+        <v>131688034</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G93">
-        <v>1701</v>
-      </c>
-      <c r="H93">
-        <v>1004</v>
+        <v>2279</v>
+      </c>
+      <c r="H93" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="L93" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L93" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>131015566</v>
+        <v>131823473</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G94">
-        <v>1701</v>
+        <v>2279</v>
       </c>
       <c r="H94">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>106</v>
       </c>
       <c r="L94" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>131025803</v>
+        <v>131828640</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G95">
-        <v>1701</v>
+        <v>2279</v>
       </c>
       <c r="H95">
-        <v>998</v>
+        <v>1021</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>107</v>
       </c>
       <c r="L95" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>131027683</v>
+        <v>131831571</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G96">
-        <v>1701</v>
+        <v>2279</v>
       </c>
       <c r="H96">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>108</v>
       </c>
       <c r="L96" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>131068607</v>
+        <v>131833378</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G97">
-        <v>1701</v>
+        <v>2279</v>
       </c>
       <c r="H97">
-        <v>996</v>
+        <v>1012</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>109</v>
       </c>
       <c r="L97" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>131072174</v>
+        <v>131836045</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G98">
-        <v>1701</v>
+        <v>2279</v>
       </c>
       <c r="H98">
-        <v>1006</v>
+        <v>1033</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>110</v>
       </c>
       <c r="L98" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>131005866</v>
+        <v>131682912</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G99">
-        <v>1701</v>
+        <v>8002</v>
       </c>
       <c r="H99">
-        <v>996</v>
+        <v>1036</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>111</v>
       </c>
       <c r="L99" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>131006640</v>
+        <v>131674849</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -4703,25 +4553,25 @@
       <c r="G100">
         <v>1701</v>
       </c>
-      <c r="H100">
-        <v>1010</v>
+      <c r="H100" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L100" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L100" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>131009875</v>
+        <v>131687163</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -4732,25 +4582,25 @@
       <c r="G101">
         <v>1701</v>
       </c>
-      <c r="H101">
-        <v>1008</v>
+      <c r="H101" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="L101" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L101" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>131014915</v>
+        <v>131698087</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -4761,25 +4611,25 @@
       <c r="G102">
         <v>1701</v>
       </c>
-      <c r="H102">
-        <v>998</v>
+      <c r="H102" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="L102" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L102" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>131020466</v>
+        <v>131704140</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -4790,25 +4640,25 @@
       <c r="G103">
         <v>1701</v>
       </c>
-      <c r="H103">
-        <v>1006</v>
+      <c r="H103" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K103" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="L103" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L103" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>131020848</v>
+        <v>131715721</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -4819,25 +4669,25 @@
       <c r="G104">
         <v>1701</v>
       </c>
-      <c r="H104">
-        <v>1004</v>
+      <c r="H104" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="L104" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L104" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>131022816</v>
+        <v>131720424</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -4848,25 +4698,25 @@
       <c r="G105">
         <v>1701</v>
       </c>
-      <c r="H105">
-        <v>1006</v>
+      <c r="H105" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K105" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="L105" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L105" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>131025664</v>
+        <v>131734439</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -4877,25 +4727,25 @@
       <c r="G106">
         <v>1701</v>
       </c>
-      <c r="H106">
-        <v>1006</v>
+      <c r="H106" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="L106" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L106" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>131027239</v>
+        <v>131740467</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -4906,25 +4756,25 @@
       <c r="G107">
         <v>1701</v>
       </c>
-      <c r="H107">
-        <v>1004</v>
+      <c r="H107" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="L107" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L107" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>131039823</v>
+        <v>131741664</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -4935,25 +4785,25 @@
       <c r="G108">
         <v>1701</v>
       </c>
-      <c r="H108">
-        <v>998</v>
+      <c r="H108" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="L108" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L108" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>131050272</v>
+        <v>131752360</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -4964,25 +4814,25 @@
       <c r="G109">
         <v>1701</v>
       </c>
-      <c r="H109">
-        <v>998</v>
+      <c r="H109" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="L109" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L109" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>131054047</v>
+        <v>131790191</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -4993,25 +4843,25 @@
       <c r="G110">
         <v>1701</v>
       </c>
-      <c r="H110">
-        <v>998</v>
+      <c r="H110" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="L110" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L110" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>131057778</v>
+        <v>131806276</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -5022,25 +4872,25 @@
       <c r="G111">
         <v>1701</v>
       </c>
-      <c r="H111">
-        <v>1010</v>
+      <c r="H111" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="L111" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L111" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>131069811</v>
+        <v>131660814</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -5051,25 +4901,25 @@
       <c r="G112">
         <v>1701</v>
       </c>
-      <c r="H112">
-        <v>1010</v>
+      <c r="H112" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="L112" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L112" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>131078134</v>
+        <v>131660838</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -5080,25 +4930,25 @@
       <c r="G113">
         <v>1701</v>
       </c>
-      <c r="H113">
-        <v>996</v>
+      <c r="H113" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="L113" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L113" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>131080649</v>
+        <v>131661961</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -5109,25 +4959,25 @@
       <c r="G114">
         <v>1701</v>
       </c>
-      <c r="H114">
-        <v>1010</v>
+      <c r="H114" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="L114" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L114" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>131137774</v>
+        <v>131661973</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -5136,27 +4986,27 @@
         <v>2002</v>
       </c>
       <c r="G115">
-        <v>2279</v>
-      </c>
-      <c r="H115">
-        <v>996</v>
+        <v>1701</v>
+      </c>
+      <c r="H115" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K115" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L115" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L115" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>131139539</v>
+        <v>131662359</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -5165,25 +5015,316 @@
         <v>2002</v>
       </c>
       <c r="G116">
-        <v>2279</v>
-      </c>
-      <c r="H116">
-        <v>1010</v>
+        <v>1701</v>
+      </c>
+      <c r="H116" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="L116" t="s">
-        <v>240</v>
+      <c r="L116" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>131663714</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <v>2002</v>
+      </c>
+      <c r="G117">
+        <v>1701</v>
+      </c>
+      <c r="H117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J117" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K117" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="L117" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>131668337</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+      <c r="C118">
+        <v>2002</v>
+      </c>
+      <c r="G118">
+        <v>1701</v>
+      </c>
+      <c r="H118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J118" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K118" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="L118" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>131669389</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+      <c r="C119">
+        <v>2002</v>
+      </c>
+      <c r="G119">
+        <v>1701</v>
+      </c>
+      <c r="H119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J119" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K119" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="L119" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>131664172</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+      <c r="C120">
+        <v>2002</v>
+      </c>
+      <c r="G120">
+        <v>1701</v>
+      </c>
+      <c r="H120" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J120" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K120" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L120" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>131696227</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+      <c r="C121">
+        <v>2002</v>
+      </c>
+      <c r="G121">
+        <v>2279</v>
+      </c>
+      <c r="H121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J121" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K121" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="L121" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>131663553</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122">
+        <v>2002</v>
+      </c>
+      <c r="G122">
+        <v>2279</v>
+      </c>
+      <c r="H122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J122" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K122" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="L122" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>131666490</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+      <c r="C123">
+        <v>2002</v>
+      </c>
+      <c r="G123">
+        <v>2279</v>
+      </c>
+      <c r="H123" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J123" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K123" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="L123" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>131711911</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124">
+        <v>2002</v>
+      </c>
+      <c r="G124">
+        <v>2279</v>
+      </c>
+      <c r="H124" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J124" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K124" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="L124" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>131765255</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <v>2002</v>
+      </c>
+      <c r="G125">
+        <v>2279</v>
+      </c>
+      <c r="H125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J125" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K125" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="L125" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>131804323</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>2002</v>
+      </c>
+      <c r="G126">
+        <v>2279</v>
+      </c>
+      <c r="H126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J126" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K126" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="L126" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A2"/>
   </sortState>
